--- a/data/hockey_scp_master.xlsx
+++ b/data/hockey_scp_master.xlsx
@@ -448,11 +448,6 @@
           <t>2018 Leaf Ultimate</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>https://www.sportscardspro.com/console/hockey-cards-2018-leaf-ultimate</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -783,11 +778,6 @@
           <t>2018 Upper Deck Ultimate Collection</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>https://www.sportscardspro.com/console/hockey-cards-2018-upper-deck-ultimate-collection</t>
-        </is>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -795,11 +785,6 @@
           <t>2019 Leaf In The Game Used</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>https://www.sportscardspro.com/console/hockey-cards-2019-leaf-in-the-game-used</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -807,11 +792,6 @@
           <t>2019 Leaf Lumber Kings</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>https://www.sportscardspro.com/console/hockey-cards-2019-leaf-lumber-kings</t>
-        </is>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -836,11 +816,6 @@
           <t>2019 Leaf Ultimate</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>https://www.sportscardspro.com/console/hockey-cards-2019-leaf-ultimate</t>
-        </is>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -882,11 +857,6 @@
           <t>2019 Panini Chronicles</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>https://www.sportscardspro.com/console/hockey-cards-2019-panini-chronicles</t>
-        </is>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -911,11 +881,6 @@
           <t>2019 Panini Immaculate Collection</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>https://www.sportscardspro.com/console/hockey-cards-2019-panini-immaculate-collection</t>
-        </is>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -940,11 +905,6 @@
           <t>2019 Panini Prime</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>https://www.sportscardspro.com/console/hockey-cards-2019-panini-prime</t>
-        </is>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1173,11 +1133,6 @@
           <t>2019 Upper Deck Clear Cut</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>https://www.sportscardspro.com/console/hockey-cards-2019-upper-deck-clear-cut</t>
-        </is>
-      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1338,11 +1293,6 @@
           <t>2019 Upper Deck Ultimate Collection</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>https://www.sportscardspro.com/console/hockey-cards-2019-upper-deck-ultimate-collection</t>
-        </is>
-      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1350,11 +1300,6 @@
           <t>2021 Fleer Ultra</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>https://www.sportscardspro.com/console/hockey-cards-2021-fleer-ultra</t>
-        </is>
-      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1362,11 +1307,6 @@
           <t>2021 Leaf Lumber</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>https://www.sportscardspro.com/console/hockey-cards-2021-leaf-lumber</t>
-        </is>
-      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1374,11 +1314,6 @@
           <t>2021 Leaf Signature Series</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>https://www.sportscardspro.com/console/hockey-cards-2021-leaf-signature-series</t>
-        </is>
-      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1386,11 +1321,6 @@
           <t>2021 Leaf Superlative</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>https://www.sportscardspro.com/console/hockey-cards-2021-leaf-superlative</t>
-        </is>
-      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1755,11 +1685,6 @@
           <t>2021 Upper Deck Ultimate Collection</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>https://www.sportscardspro.com/console/hockey-cards-2021-upper-deck-ultimate-collection</t>
-        </is>
-      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -1784,11 +1709,6 @@
           <t>2022 Leaf In The Game Used</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>https://www.sportscardspro.com/console/hockey-cards-2022-leaf-in-the-game-used</t>
-        </is>
-      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -2085,11 +2005,6 @@
           <t>2022 Upper Deck Ovation</t>
         </is>
       </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>https://www.sportscardspro.com/console/hockey-cards-2022-upper-deck-ovation</t>
-        </is>
-      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -2507,7 +2422,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>https://www.sportscardspro.com/console/hockey-cards-2023-upper-deck-ice</t>
+          <t>https://www.sportscardspro.com/console/hockey-cards-2023-upper-deck-ice-hockey</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>https://www.sportscardspro.com/price-guide/download-custom?t=7f389d8e7c6dbb986abeec5f5789ac4a0a4cac15&amp;console-uids=G73260</t>
         </is>
       </c>
     </row>
@@ -3027,11 +2947,6 @@
           <t>2024 Upper Deck Ultimate Collection</t>
         </is>
       </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>https://www.sportscardspro.com/console/hockey-cards-2024-upper-deck-ultimate-collection</t>
-        </is>
-      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -3107,11 +3022,6 @@
           <t>2025 Parkhurst</t>
         </is>
       </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>https://www.sportscardspro.com/console/hockey-cards-2025-parkhurst</t>
-        </is>
-      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -3136,11 +3046,6 @@
           <t>2025 Sp</t>
         </is>
       </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>https://www.sportscardspro.com/console/hockey-cards-2025-sp</t>
-        </is>
-      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -3267,11 +3172,6 @@
           <t>2025 Upper Deck Clear Cut</t>
         </is>
       </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>https://www.sportscardspro.com/console/hockey-cards-2025-upper-deck-clear-cut</t>
-        </is>
-      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -3296,11 +3196,6 @@
           <t>2025 Upper Deck Ice</t>
         </is>
       </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>https://www.sportscardspro.com/console/hockey-cards-2025-upper-deck-ice</t>
-        </is>
-      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -3325,11 +3220,6 @@
           <t>2025 Upper Deck Premier</t>
         </is>
       </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>https://www.sportscardspro.com/console/hockey-cards-2025-upper-deck-premier</t>
-        </is>
-      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -3337,21 +3227,11 @@
           <t>2025 Upper Deck Stature</t>
         </is>
       </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>https://www.sportscardspro.com/console/hockey-cards-2025-upper-deck-stature</t>
-        </is>
-      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
           <t>2025 Upper Deck Ultimate Collection</t>
-        </is>
-      </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>https://www.sportscardspro.com/console/hockey-cards-2025-upper-deck-ultimate-collection</t>
         </is>
       </c>
     </row>
